--- a/saida/estat-desc.xlsx
+++ b/saida/estat-desc.xlsx
@@ -455,13 +455,13 @@
         <v>5.64037</v>
       </c>
       <c r="F2">
-        <v>-0.1220782820340076</v>
+        <v>0.88507908</v>
       </c>
       <c r="G2">
-        <v>0.1851924318856376</v>
+        <v>1.20345</v>
       </c>
       <c r="H2">
-        <v>1.073085995362522</v>
+        <v>2.924390244</v>
       </c>
       <c r="I2">
         <v>1.256036577</v>
@@ -476,7 +476,7 @@
         <v>6.698174945</v>
       </c>
       <c r="M2">
-        <v>1.661941169960929</v>
+        <v>5.269529976</v>
       </c>
       <c r="N2">
         <v>23.76701535</v>
@@ -507,13 +507,13 @@
         <v>10.98094</v>
       </c>
       <c r="F3">
-        <v>2.241879217876651</v>
+        <v>9.411</v>
       </c>
       <c r="G3">
-        <v>1.429339482661028</v>
+        <v>4.17594</v>
       </c>
       <c r="H3">
-        <v>2.845903587970234</v>
+        <v>17.21710887</v>
       </c>
       <c r="I3">
         <v>6.937585174500001</v>
@@ -528,7 +528,7 @@
         <v>12.80659271</v>
       </c>
       <c r="M3">
-        <v>3.27765489061674</v>
+        <v>26.51352266</v>
       </c>
       <c r="N3">
         <v>42.126448205</v>
@@ -537,7 +537,7 @@
         <v>61.65817866499999</v>
       </c>
       <c r="P3">
-        <v>0.2338687834909811</v>
+        <v>0.263478736</v>
       </c>
     </row>
     <row r="4">
@@ -559,13 +559,13 @@
         <v>12.8642</v>
       </c>
       <c r="F4">
-        <v>2.53261845495953</v>
+        <v>12.58642</v>
       </c>
       <c r="G4">
-        <v>1.768431133921408</v>
+        <v>5.86165</v>
       </c>
       <c r="H4">
-        <v>3.054542760940836</v>
+        <v>21.21148459</v>
       </c>
       <c r="I4">
         <v>8.849670286</v>
@@ -580,7 +580,7 @@
         <v>14.91123705</v>
       </c>
       <c r="M4">
-        <v>3.482452810307652</v>
+        <v>32.53943734</v>
       </c>
       <c r="N4">
         <v>48.26021995</v>
@@ -589,7 +589,7 @@
         <v>68.49319713</v>
       </c>
       <c r="P4">
-        <v>0.7900228974531521</v>
+        <v>1.203446879</v>
       </c>
     </row>
     <row r="5">
@@ -611,13 +611,13 @@
         <v>13.24515740152309</v>
       </c>
       <c r="F5">
-        <v>2.585293048743411</v>
+        <v>15.69606405226033</v>
       </c>
       <c r="G5">
-        <v>1.799225278307134</v>
+        <v>6.945618583173643</v>
       </c>
       <c r="H5">
-        <v>3.033319392986758</v>
+        <v>21.94765817639832</v>
       </c>
       <c r="I5">
         <v>9.139074824984192</v>
@@ -632,7 +632,7 @@
         <v>15.70910344970645</v>
       </c>
       <c r="M5">
-        <v>3.461918999742062</v>
+        <v>33.51096531051796</v>
       </c>
       <c r="N5">
         <v>49.21830735117742</v>
@@ -641,7 +641,7 @@
         <v>67.0083417531326</v>
       </c>
       <c r="P5">
-        <v>0.8789996743474416</v>
+        <v>2.482425511391575</v>
       </c>
     </row>
     <row r="6">
@@ -663,13 +663,13 @@
         <v>15</v>
       </c>
       <c r="F6">
-        <v>2.916134230409325</v>
+        <v>18.46975</v>
       </c>
       <c r="G6">
-        <v>2.116578350490463</v>
+        <v>8.302679999999999</v>
       </c>
       <c r="H6">
-        <v>3.240149530517607</v>
+        <v>25.53754045</v>
       </c>
       <c r="I6">
         <v>11.05815684</v>
@@ -684,7 +684,7 @@
         <v>17.72657843</v>
       </c>
       <c r="M6">
-        <v>3.667908475583582</v>
+        <v>39.16989543</v>
       </c>
       <c r="N6">
         <v>54.679592955</v>
@@ -693,7 +693,7 @@
         <v>73.849426655</v>
       </c>
       <c r="P6">
-        <v>1.312401257989585</v>
+        <v>2.715083907</v>
       </c>
     </row>
     <row r="7">
@@ -715,13 +715,13 @@
         <v>41.5704</v>
       </c>
       <c r="F7">
-        <v>5.185451198263543</v>
+        <v>178.65404</v>
       </c>
       <c r="G7">
-        <v>4.749995461940349</v>
+        <v>115.58376</v>
       </c>
       <c r="H7">
-        <v>5.406727833920977</v>
+        <v>222.9010239</v>
       </c>
       <c r="I7">
         <v>43.39912281</v>
@@ -736,7 +736,7 @@
         <v>57.39487956</v>
       </c>
       <c r="M7">
-        <v>5.477042921303153</v>
+        <v>239.1385094</v>
       </c>
       <c r="N7">
         <v>250.1258647</v>
@@ -745,7 +745,7 @@
         <v>95.60726944</v>
       </c>
       <c r="P7">
-        <v>4.235963069389168</v>
+        <v>68.12822196</v>
       </c>
     </row>
     <row r="8">
@@ -767,13 +767,13 @@
         <v>3.213383286180583</v>
       </c>
       <c r="F8">
-        <v>0.552114846244074</v>
+        <v>11.74580919842028</v>
       </c>
       <c r="G8">
-        <v>0.5028748795679326</v>
+        <v>4.688292983434976</v>
       </c>
       <c r="H8">
-        <v>0.3330605087594253</v>
+        <v>8.245785876178282</v>
       </c>
       <c r="I8">
         <v>3.228850736598275</v>
@@ -788,7 +788,7 @@
         <v>4.1620316211645</v>
       </c>
       <c r="M8">
-        <v>0.3198411989916015</v>
+        <v>11.20454707261358</v>
       </c>
       <c r="N8">
         <v>10.93385355782002</v>
@@ -797,7 +797,7 @@
         <v>9.848021017795871</v>
       </c>
       <c r="P8">
-        <v>0.7534230751781256</v>
+        <v>4.827730292311481</v>
       </c>
     </row>
     <row r="9">
@@ -819,13 +819,13 @@
         <v>24.26081615165305</v>
       </c>
       <c r="F9">
-        <v>21.35598695522858</v>
+        <v>74.83283171699858</v>
       </c>
       <c r="G9">
-        <v>27.94952281023312</v>
+        <v>67.50000633194526</v>
       </c>
       <c r="H9">
-        <v>10.98006723358852</v>
+        <v>37.5702310009798</v>
       </c>
       <c r="I9">
         <v>35.3301707058062</v>
@@ -840,7 +840,7 @@
         <v>26.49439310454266</v>
       </c>
       <c r="M9">
-        <v>9.238841203836136</v>
+        <v>33.43546498523827</v>
       </c>
       <c r="N9">
         <v>22.21501336851329</v>
@@ -849,7 +849,7 @@
         <v>14.69670903673046</v>
       </c>
       <c r="P9">
-        <v>85.71369218509182</v>
+        <v>194.4763405853494</v>
       </c>
     </row>
     <row r="10">
@@ -871,13 +871,13 @@
         <v>1.14632232665418</v>
       </c>
       <c r="F10">
-        <v>0.3820822965038484</v>
+        <v>4.847928032376979</v>
       </c>
       <c r="G10">
-        <v>0.4610620817520036</v>
+        <v>6.651223328770114</v>
       </c>
       <c r="H10">
-        <v>-0.2831555119173085</v>
+        <v>5.92397895029749</v>
       </c>
       <c r="I10">
         <v>1.04559151931071</v>
@@ -892,7 +892,7 @@
         <v>1.609074521216833</v>
       </c>
       <c r="M10">
-        <v>-0.4055664289671351</v>
+        <v>3.169908634492198</v>
       </c>
       <c r="N10">
         <v>3.168654248967359</v>
@@ -901,7 +901,7 @@
         <v>-0.9762066535846425</v>
       </c>
       <c r="P10">
-        <v>0.9660524423219697</v>
+        <v>5.954743606246703</v>
       </c>
     </row>
     <row r="11">
@@ -923,13 +923,13 @@
         <v>4.346268017019701</v>
       </c>
       <c r="F11">
-        <v>1.232493208860362</v>
+        <v>44.35930435977211</v>
       </c>
       <c r="G11">
-        <v>0.7120911743193958</v>
+        <v>111.2318857403898</v>
       </c>
       <c r="H11">
-        <v>2.80797794487498</v>
+        <v>112.1662010330672</v>
       </c>
       <c r="I11">
         <v>5.725034491201114</v>
@@ -944,7 +944,7 @@
         <v>5.99742337922342</v>
       </c>
       <c r="M11">
-        <v>2.282094402684313</v>
+        <v>40.81701420355797</v>
       </c>
       <c r="N11">
         <v>40.09640989981276</v>
@@ -953,7 +953,7 @@
         <v>1.877065855124823</v>
       </c>
       <c r="P11">
-        <v>1.191874762356495</v>
+        <v>49.97232312546469</v>
       </c>
     </row>
   </sheetData>
